--- a/Scales-pas/PASS-process/Petri-Romão_2024_PASS-process_GER.xlsx
+++ b/Scales-pas/PASS-process/Petri-Romão_2024_PASS-process_GER.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\Papoula\Research\PHD\Projects\Organising all questionnaires\PAS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Papoula\Desktop\git_repositories\github_personal\positive-appraisal-style-methods\Scales-pas\PASS-process\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{267C6F2B-1108-41C6-8D2E-3D9F301BD9DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42B213A3-53E9-41DE-891C-09E0C13861A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="17472" windowHeight="10992" xr2:uid="{2243D91A-F1AD-4BAA-BD82-86E6A3DB83B8}"/>
+    <workbookView xWindow="-78" yWindow="0" windowWidth="8796" windowHeight="10878" xr2:uid="{2243D91A-F1AD-4BAA-BD82-86E6A3DB83B8}"/>
   </bookViews>
   <sheets>
     <sheet name="PASS-process GER" sheetId="1" r:id="rId1"/>
@@ -54,9 +54,6 @@
     <t>Ich denke, dass ich akzeptieren muss, was passiert ist.</t>
   </si>
   <si>
-    <t>Ich denke an schönere Dinge als an das, was ich erlebt habe.</t>
-  </si>
-  <si>
     <t>Ich denke, dass ich die Situation akzeptieren muss.</t>
   </si>
   <si>
@@ -76,6 +73,9 @@
   </si>
   <si>
     <t>PASS-process</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ich denke, dass ich aufgrund dessen, was geschehen ist, ein stärkerer Mensch werden kann. </t>
   </si>
 </sst>
 </file>
@@ -544,7 +544,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="158.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="4" t="s">
@@ -596,7 +596,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="9"/>
@@ -608,7 +608,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="9"/>
@@ -620,7 +620,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D7" s="8"/>
       <c r="E7" s="9"/>
@@ -632,7 +632,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="9"/>
@@ -644,7 +644,7 @@
         <v>8</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="9"/>
@@ -656,7 +656,7 @@
         <v>9</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -665,7 +665,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D11" s="8"/>
       <c r="E11" s="9"/>
